--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/johansen_Gasolina_IPCA_Transporte.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/johansen_Gasolina_IPCA_Transporte.xlsx
@@ -440,7 +440,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>163.5892249967955</v>
+        <v>163.5892249967958</v>
       </c>
       <c r="B2" t="n">
         <v>120.3673</v>
@@ -454,7 +454,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96.29835009972044</v>
+        <v>96.29835009972128</v>
       </c>
       <c r="B3" t="n">
         <v>91.10899999999999</v>
@@ -468,7 +468,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55.90649936546468</v>
+        <v>55.90649936546447</v>
       </c>
       <c r="B4" t="n">
         <v>65.8202</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>33.20401684277367</v>
+        <v>33.20401684277341</v>
       </c>
       <c r="B5" t="n">
         <v>44.4929</v>
@@ -496,7 +496,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21.25821140562166</v>
+        <v>21.2582114056215</v>
       </c>
       <c r="B6" t="n">
         <v>27.0669</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11.31655394779154</v>
+        <v>11.31655394779141</v>
       </c>
       <c r="B7" t="n">
         <v>13.4294</v>
@@ -524,7 +524,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.637846281233775</v>
+        <v>2.637846281233675</v>
       </c>
       <c r="B8" t="n">
         <v>2.7055</v>
